--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934491</v>
       </c>
       <c r="B2" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97253</v>
+        <v>97257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934491</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97257</v>
+        <v>97264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97272</v>
+        <v>97277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97277</v>
+        <v>97280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934493</v>
+        <v>128934496</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
         <v>552108</v>
       </c>
       <c r="R8" t="n">
-        <v>6519491</v>
+        <v>6519546</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934496</v>
+        <v>128934493</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>552108</v>
       </c>
       <c r="R9" t="n">
-        <v>6519546</v>
+        <v>6519491</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934491</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97280</v>
+        <v>97290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934496</v>
+        <v>128934493</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
         <v>552108</v>
       </c>
       <c r="R8" t="n">
-        <v>6519546</v>
+        <v>6519491</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934493</v>
+        <v>128934496</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>552108</v>
       </c>
       <c r="R9" t="n">
-        <v>6519491</v>
+        <v>6519546</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97290</v>
+        <v>97297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934491</v>
       </c>
       <c r="B2" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97297</v>
+        <v>97299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97299</v>
+        <v>97325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>97337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>128934492</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128934494</v>
       </c>
       <c r="B4" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>128934489</v>
       </c>
       <c r="B5" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128934488</v>
       </c>
       <c r="B6" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128934486</v>
       </c>
       <c r="B7" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934493</v>
+        <v>128934496</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
         <v>552108</v>
       </c>
       <c r="R8" t="n">
-        <v>6519491</v>
+        <v>6519546</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934496</v>
+        <v>128934493</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         <v>552108</v>
       </c>
       <c r="R9" t="n">
-        <v>6519546</v>
+        <v>6519491</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -1307,6 +1307,15 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordost om Sand, Ög</t>
@@ -1357,6 +1366,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,6 +1414,15 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordost om Sand, Ög</t>
@@ -1454,6 +1473,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>128934496</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128934493</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128934491</v>
+        <v>128934489</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordost om Sand, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552047</v>
+        <v>552044</v>
       </c>
       <c r="R2" t="n">
-        <v>6519539</v>
+        <v>6519564</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vilande i gammal tall. Flög iväg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128934492</v>
+        <v>128934494</v>
       </c>
       <c r="B3" t="n">
-        <v>91571</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552107</v>
+        <v>552111</v>
       </c>
       <c r="R3" t="n">
-        <v>6519479</v>
+        <v>6519496</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -890,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128934494</v>
+        <v>128934486</v>
       </c>
       <c r="B4" t="n">
-        <v>96213</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552111</v>
+        <v>552092</v>
       </c>
       <c r="R4" t="n">
-        <v>6519496</v>
+        <v>6519548</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934489</v>
+        <v>128934488</v>
       </c>
       <c r="B5" t="n">
-        <v>96213</v>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552044</v>
+        <v>552066</v>
       </c>
       <c r="R5" t="n">
-        <v>6519564</v>
+        <v>6519554</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934488</v>
+        <v>128934492</v>
       </c>
       <c r="B6" t="n">
-        <v>97006</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552066</v>
+        <v>552107</v>
       </c>
       <c r="R6" t="n">
-        <v>6519554</v>
+        <v>6519479</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1181,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934486</v>
+        <v>128934491</v>
       </c>
       <c r="B7" t="n">
-        <v>97345</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,34 +1171,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordost om Sand, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552092</v>
+        <v>552047</v>
       </c>
       <c r="R7" t="n">
-        <v>6519548</v>
+        <v>6519539</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1252,6 +1247,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vilande i gammal tall. Flög iväg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934496</v>
+        <v>128934493</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>552108</v>
       </c>
       <c r="R8" t="n">
-        <v>6519546</v>
+        <v>6519491</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934493</v>
+        <v>128934496</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>552108</v>
       </c>
       <c r="R9" t="n">
-        <v>6519491</v>
+        <v>6519546</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 18262-2024 artfynd.xlsx
+++ b/artfynd/A 18262-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934489</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934486</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934492</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934491</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,8 +1529,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>